--- a/reports/marketing_spend_mock_2026-03.xlsx
+++ b/reports/marketing_spend_mock_2026-03.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marketplace Fees &amp; Commissions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FBA Cost of Sales" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ad Spend" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Data (samples)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FBA Returns &amp; Removals" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancellations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ad Spend" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Data" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="£#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,7 +59,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000D47A1"/>
+      <color rgb="002E7D32"/>
       <sz val="10"/>
     </font>
     <font>
@@ -68,7 +69,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00E65100"/>
+      <color rgb="000D47A1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -77,13 +78,8 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00212121"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
       <color rgb="00757575"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="12">
@@ -120,12 +116,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001565C0"/>
+        <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000D47A1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
       </patternFill>
     </fill>
     <fill>
@@ -138,13 +139,8 @@
         <fgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -157,11 +153,20 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -217,43 +222,24 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -265,71 +251,61 @@
     <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="3" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -696,13 +672,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -726,7 +702,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>% of Gross Revenue</t>
+          <t>% of Net Revenue</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -738,7 +714,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Gross Revenue (all channels)</t>
+          <t>Net Revenue (all channels, ex-VAT)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
@@ -749,7 +725,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Shopify + eBay + Amazon + ManoMano + OnBuy + B&amp;Q</t>
+          <t>Shopify Direct + eBay + Amazon + ManoMano + OnBuy + B&amp;Q (20% UK VAT backed out)</t>
         </is>
       </c>
     </row>
@@ -775,18 +751,18 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Amazon FBA cost of sales</t>
+          <t>Commission paid to Wayne Theisinger</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>11759</v>
+        <v>18750.5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.02699278065352876</v>
+        <v>0.04304176661654826</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Fulfilment, storage, inbound, prep — see FBA Cost of Sales tab</t>
+          <t>Invoiced Value</t>
         </is>
       </c>
     </row>
@@ -812,14 +788,14 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Total deductions (fees + FBA + ads)</t>
+          <t>Total deductions (fees + commission + ads)</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>69713</v>
+        <v>76704.5</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.160026168696271</v>
+        <v>0.1760751546592905</v>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
@@ -830,18 +806,18 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Net contribution</t>
+          <t>Contribution after deductions</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>365922</v>
+        <v>358930.5</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.839973831303729</v>
+        <v>0.8239248453407095</v>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Gross revenue after all marketplace costs</t>
+          <t>Net revenue minus all marketplace costs.</t>
         </is>
       </c>
     </row>
@@ -860,7 +836,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Gross Revenue (£)</t>
+          <t>Net Revenue (£)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -987,215 +963,115 @@
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Amazon FBA Cost of Sales</t>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ad Spend by Platform</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>Cost Type</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>Amount (£)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>% of Amazon Revenue</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Spend (£)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>% of Net Revenue</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Note / Coverage</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>FBA fulfilment fees (pick, pack &amp; ship)</t>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>8713</v>
+        <v>15247</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>0.1000034432495093</v>
-      </c>
-      <c r="D25" s="21" t="inlineStr"/>
+        <v>0.0349994835125736</v>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>FBA storage fees (standard, March)</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="n">
-        <v>1218</v>
-      </c>
-      <c r="C26" s="24" t="n">
-        <v>0.013979593007908</v>
-      </c>
-      <c r="D26" s="25" t="inlineStr"/>
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>eBay Promoted Listings</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>2178</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.004999598287557244</v>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>FBA inbound shipping (stock to warehouse)</t>
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Amazon Sponsored Products</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>1480</v>
+        <v>3050</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>0.0169866975793956</v>
-      </c>
-      <c r="D27" s="21" t="inlineStr"/>
+        <v>0.007001274002318454</v>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>FBA prep &amp; labelling</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="n">
-        <v>348</v>
-      </c>
-      <c r="C28" s="24" t="n">
-        <v>0.003994169430830856</v>
-      </c>
-      <c r="D28" s="25" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>TOTAL FBA COST OF SALES</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="n">
-        <v>11759</v>
-      </c>
-      <c r="C29" s="28" t="n">
-        <v>0.1349639032676438</v>
-      </c>
-      <c r="D29" s="29" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Ad Spend by Platform</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Spend (£)</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>% of Gross Revenue</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>Google Ads (PMax + Shopping)</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n">
-        <v>15247</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>0.0349994835125736</v>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Campaign detail in Ad Spend tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>eBay Promoted Listings</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>2178</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>0.004999598287557244</v>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Charged as AD_FEE via eBay Finances API</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>Amazon Sponsored Products</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n">
-        <v>3050</v>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>0.007001274002318454</v>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Via Amazon Advertising API</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n">
+      <c r="B28" s="12" t="n">
         <v>20475</v>
       </c>
-      <c r="C36" s="13" t="n">
+      <c r="C28" s="13" t="n">
         <v>0.0470003558024493</v>
       </c>
-      <c r="D36" s="30" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
-        <is>
-          <t>⚠  MOCK DATA — illustrative figures based on 2026 plan projections. Replace with live API data before sharing with funders.</t>
+      <c r="D28" s="20" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>⚠  MOCK / DRY-RUN DATA — replace with live API credentials before sharing with funders.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A38:D38"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1207,13 +1083,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -1245,12 +1121,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Channel Revenue (£)</t>
+          <t>Net Channel Revenue (£)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Fee as % of Revenue</t>
+          <t>Fee as % of Net Revenue</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1289,9 +1165,9 @@
           <t>Shopify GraphQL (mock)</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1177,7 @@
           <t>Shopify Direct subtotal</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n"/>
+      <c r="B5" s="20" t="n"/>
       <c r="C5" s="12" t="n">
         <v>2614</v>
       </c>
@@ -1311,8 +1187,8 @@
       <c r="E5" s="13" t="n">
         <v>0.01500109036234462</v>
       </c>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
@@ -1339,9 +1215,9 @@
           <t>eBay Finances API (mock)</t>
         </is>
       </c>
-      <c r="G6" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -1355,16 +1231,12 @@
       <c r="C7" s="8" t="n">
         <v>2178</v>
       </c>
-      <c r="D7" s="8" t="n"/>
+      <c r="D7" s="22" t="n"/>
       <c r="E7" s="9" t="n">
         <v>0.01999834724402942</v>
       </c>
       <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
-        </is>
-      </c>
+      <c r="G7" s="23" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr"/>
@@ -1376,16 +1248,12 @@
       <c r="C8" s="4" t="n">
         <v>891</v>
       </c>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="24" t="n"/>
       <c r="E8" s="5" t="n">
         <v>0.008181142054375671</v>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
-        </is>
-      </c>
+      <c r="G8" s="25" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr"/>
@@ -1397,16 +1265,12 @@
       <c r="C9" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="22" t="n"/>
       <c r="E9" s="9" t="n">
         <v>0.0004499169031025902</v>
       </c>
       <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
-        </is>
-      </c>
+      <c r="G9" s="23" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
@@ -1414,7 +1278,7 @@
           <t>eBay subtotal</t>
         </is>
       </c>
-      <c r="B10" s="30" t="n"/>
+      <c r="B10" s="20" t="n"/>
       <c r="C10" s="12" t="n">
         <v>15098</v>
       </c>
@@ -1424,8 +1288,8 @@
       <c r="E10" s="13" t="n">
         <v>0.1386294980212838</v>
       </c>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -1452,9 +1316,9 @@
           <t>SP-API Settlement (mock)</t>
         </is>
       </c>
-      <c r="G11" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1328,7 @@
           <t>Amazon subtotal</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n"/>
+      <c r="B12" s="20" t="n"/>
       <c r="C12" s="12" t="n">
         <v>10455</v>
       </c>
@@ -1474,8 +1338,8 @@
       <c r="E12" s="13" t="n">
         <v>0.1199972454003925</v>
       </c>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="30" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -1502,9 +1366,9 @@
           <t>BaseLinker (mock)</t>
         </is>
       </c>
-      <c r="G13" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1378,7 @@
           <t>ManoMano subtotal</t>
         </is>
       </c>
-      <c r="B14" s="30" t="n"/>
+      <c r="B14" s="20" t="n"/>
       <c r="C14" s="12" t="n">
         <v>6273</v>
       </c>
@@ -1524,8 +1388,8 @@
       <c r="E14" s="13" t="n">
         <v>0.1799948351553757</v>
       </c>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="30" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -1552,9 +1416,9 @@
           <t>BaseLinker (mock)</t>
         </is>
       </c>
-      <c r="G15" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1428,7 @@
           <t>OnBuy subtotal</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n"/>
+      <c r="B16" s="20" t="n"/>
       <c r="C16" s="12" t="n">
         <v>1220</v>
       </c>
@@ -1574,8 +1438,8 @@
       <c r="E16" s="13" t="n">
         <v>0.07001434720229555</v>
       </c>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -1602,9 +1466,9 @@
           <t>Mirakl API (mock)</t>
         </is>
       </c>
-      <c r="G17" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -1618,16 +1482,12 @@
       <c r="C18" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="D18" s="4" t="n"/>
+      <c r="D18" s="24" t="n"/>
       <c r="E18" s="5" t="n">
         <v>0.009182033820491238</v>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
-        </is>
-      </c>
+      <c r="G18" s="25" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
@@ -1635,7 +1495,7 @@
           <t>B&amp;Q (Mirakl) subtotal</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n"/>
+      <c r="B19" s="20" t="n"/>
       <c r="C19" s="12" t="n">
         <v>1819</v>
       </c>
@@ -1645,47 +1505,39 @@
       <c r="E19" s="13" t="n">
         <v>0.1391843293289464</v>
       </c>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="30" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="20" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>GRAND TOTAL — MARKETPLACE FEES</t>
         </is>
       </c>
-      <c r="B20" s="34" t="n"/>
-      <c r="C20" s="35" t="n">
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="28" t="n">
         <v>37479</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="28" t="n">
         <v>435635</v>
       </c>
-      <c r="E20" s="36" t="n">
+      <c r="E20" s="29" t="n">
         <v>0.08603303224029291</v>
       </c>
-      <c r="F20" s="34" t="n"/>
-      <c r="G20" s="34" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="31" t="inlineStr">
-        <is>
-          <t>⚠  MOCK DATA — illustrative figures based on 2026 plan projections. Replace with live API data before sharing with funders.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="37" t="inlineStr">
-        <is>
-          <t>ℹ  Amazon FBA operational costs (fulfilment, storage, inbound, prep) are excluded from this tab — see 'FBA Cost of Sales' tab.</t>
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>⚠  MOCK / DRY-RUN DATA — replace with live API credentials before sharing with funders.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1697,352 +1549,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
-        <is>
-          <t>Amazon FBA — Cost of Sales  |  March 2026</t>
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>Amazon FBA — Returns, Removals &amp; Stranded Stock  |  March 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="4" customHeight="1"/>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>These are operational costs charged by Amazon for physical fulfilment of orders via FBA (Fulfilment by Amazon). They are costs of sale, not marketing spend, and are tracked separately from the marketing budget.</t>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Customer Returns Received by Amazon</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>FBA Cost Type</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>Disposition</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>Lines</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>% of Returns</t>
+        </is>
+      </c>
+      <c r="E4" s="32" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>No customer returns received this month.</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="34" t="n"/>
+      <c r="E5" s="34" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Removal Shipments (units processed by Amazon this month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>Order Type</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Shipments</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr"/>
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>No removal shipments processed this month.</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Removal &amp; Disposal Costs (from Amazon Finances)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Fee Type</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Amount (£)</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>% of Amazon Revenue</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>% of Total Gross Revenue</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr"/>
+      <c r="D11" s="32" t="inlineStr"/>
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>FBA fulfilment fees (pick, pack &amp; ship)</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>8713</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>0.1000034432495093</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0.02000068864990187</v>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>Charged per unit shipped. Varies by size/weight.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="40" t="inlineStr">
-        <is>
-          <t>FBA storage fees (standard, March)</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="n">
-        <v>1218</v>
-      </c>
-      <c r="C6" s="24" t="n">
-        <v>0.013979593007908</v>
-      </c>
-      <c r="D6" s="24" t="n">
-        <v>0.002795918601581599</v>
-      </c>
-      <c r="E6" s="41" t="inlineStr">
-        <is>
-          <t>Monthly charge based on cubic footage. Long-term storage rates apply after 365 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>FBA inbound shipping (stock to warehouse)</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>1480</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>0.0169866975793956</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0.003397339515879119</v>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Cost of sending stock from MowDirect / supplier to Amazon fulfilment centre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="40" t="inlineStr">
-        <is>
-          <t>FBA prep &amp; labelling</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="n">
-        <v>348</v>
-      </c>
-      <c r="C8" s="24" t="n">
-        <v>0.003994169430830856</v>
-      </c>
-      <c r="D8" s="24" t="n">
-        <v>0.0007988338861661712</v>
-      </c>
-      <c r="E8" s="41" t="inlineStr">
-        <is>
-          <t>Per-unit labelling, bagging, or bundling required by Amazon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
-        <is>
-          <t>TOTAL FBA COST OF SALES</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="n">
-        <v>11759</v>
-      </c>
-      <c r="C9" s="28" t="n">
-        <v>0.1349639032676438</v>
-      </c>
-      <c r="D9" s="28" t="n">
-        <v>0.02699278065352876</v>
-      </c>
-      <c r="E9" s="43" t="inlineStr"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  For reference: Amazon referral fee (commission) — on Marketplace Fees tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Fee Type</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>Amount (£)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>% of Amazon Revenue</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>Referral fees / commission (12%)</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n">
-        <v>10455</v>
-      </c>
-      <c r="C13" s="24" t="n">
-        <v>0.1199972454003925</v>
-      </c>
-      <c r="D13" s="25" t="inlineStr"/>
-      <c r="E13" s="41" t="inlineStr">
-        <is>
-          <t>Commission on each sale — treated as marketing cost of channel, not FBA operational cost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FBA Cost of Sales vs Marketing Budget — Amazon channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Cost bucket</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>Amount (£)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>% of Amazon Revenue</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="20" t="inlineStr"/>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>No removal / disposal fees billed this month.</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Current Inventory Snapshot — units sitting at Amazon today</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr"/>
+      <c r="D15" s="32" t="inlineStr"/>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>Fulfillable (sellable)</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="37" t="inlineStr"/>
+      <c r="D16" s="37" t="inlineStr"/>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>Active inventory available to ship to customers.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Amazon referral commission</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>10455</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>0.1199972454003925</v>
-      </c>
-      <c r="D17" s="21" t="inlineStr"/>
-      <c r="E17" s="21" t="inlineStr"/>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Unfulfillable</t>
+        </is>
+      </c>
+      <c r="B17" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="23" t="inlineStr"/>
+      <c r="D17" s="23" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Stranded — could be removed or disposed.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>Amazon Sponsored Products</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="n">
-        <v>3050</v>
-      </c>
-      <c r="C18" s="24" t="n">
-        <v>0.03500637001159227</v>
-      </c>
-      <c r="D18" s="25" t="inlineStr"/>
-      <c r="E18" s="25" t="inlineStr"/>
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>Researching</t>
+        </is>
+      </c>
+      <c r="B18" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="37" t="inlineStr"/>
+      <c r="D18" s="37" t="inlineStr"/>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>Lost/damaged claims under investigation by Amazon.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>FBA fulfilment fees</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>8713</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>0.1000034432495093</v>
-      </c>
-      <c r="D19" s="21" t="inlineStr"/>
-      <c r="E19" s="21" t="inlineStr"/>
+          <t>Inbound working</t>
+        </is>
+      </c>
+      <c r="B19" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="23" t="inlineStr"/>
+      <c r="D19" s="23" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Shipment created in Seller Central but not yet sent.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>FBA storage fees</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="n">
-        <v>1218</v>
-      </c>
-      <c r="C20" s="24" t="n">
-        <v>0.013979593007908</v>
-      </c>
-      <c r="D20" s="25" t="inlineStr"/>
-      <c r="E20" s="25" t="inlineStr"/>
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>Inbound shipped</t>
+        </is>
+      </c>
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="37" t="inlineStr"/>
+      <c r="D20" s="37" t="inlineStr"/>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>In transit from MowDirect/supplier to fulfilment centre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>FBA inbound shipping</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>1480</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>0.0169866975793956</v>
-      </c>
-      <c r="D21" s="21" t="inlineStr"/>
-      <c r="E21" s="21" t="inlineStr"/>
+          <t>Inbound receiving</t>
+        </is>
+      </c>
+      <c r="B21" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="23" t="inlineStr"/>
+      <c r="D21" s="23" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Arrived at FC, being checked in.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>FBA prep &amp; labelling</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="n">
-        <v>348</v>
-      </c>
-      <c r="C22" s="24" t="n">
-        <v>0.003994169430830856</v>
-      </c>
-      <c r="D22" s="25" t="inlineStr"/>
-      <c r="E22" s="25" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>TOTAL AMAZON COSTS</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="n">
-        <v>25264</v>
-      </c>
-      <c r="C23" s="28" t="n">
-        <v>0.2899675186796286</v>
-      </c>
-      <c r="D23" s="29" t="n"/>
-      <c r="E23" s="29" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>⚠  MOCK DATA — illustrative figures based on 2026 plan projections. Replace with live API data before sharing with funders.</t>
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>AVAILABLE TO BE PICKED UP / DISPOSED</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="44" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="44" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="45" t="inlineStr">
+        <is>
+          <t>ℹ  Inventory snapshot covers 0 active FBA SKUs at the time of report generation. Customer-returns and removal-shipment figures cover the reporting month only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>⚠  MOCK / DRY-RUN DATA — replace with live API credentials before sharing with funders.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A11:E11"/>
+  <mergeCells count="10">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A6:E6"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2055,22 +1868,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Paid Ad Spend  |  March 2026</t>
+          <t>Order Cancellations  |  March 2026</t>
         </is>
       </c>
     </row>
@@ -2078,199 +1889,64 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Reason / Attribution</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Spend (£)</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Impressions</t>
+          <t>Value (£)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Google Ads</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Performance Max — All Products</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>10673</v>
-      </c>
-      <c r="D4" s="44" t="n">
-        <v>1240000</v>
-      </c>
-      <c r="E4" s="44" t="n">
-        <v>18650</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.01504032258064516</v>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Shopping — Spectrum Own-Label</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>4574</v>
-      </c>
-      <c r="D5" s="45" t="n">
-        <v>380000</v>
-      </c>
-      <c r="E5" s="45" t="n">
-        <v>6920</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>0.01821052631578947</v>
-      </c>
-      <c r="G5" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>Google Ads subtotal</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="12" t="n">
-        <v>15247</v>
-      </c>
-      <c r="D6" s="46" t="n">
-        <v>1620000</v>
-      </c>
-      <c r="E6" s="46" t="n">
-        <v>25570</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>0.01578395061728395</v>
-      </c>
-      <c r="G6" s="30" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>eBay</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>eBay Promoted Listings</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>2178</v>
-      </c>
-      <c r="D7" s="45" t="n">
-        <v>412000</v>
-      </c>
-      <c r="E7" s="45" t="n">
-        <v>5340</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>0.01296116504854369</v>
-      </c>
-      <c r="G7" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Amazon Sponsored Products</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>3050</v>
-      </c>
-      <c r="D8" s="44" t="n">
-        <v>189000</v>
-      </c>
-      <c r="E8" s="44" t="n">
-        <v>3210</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.01698412698412698</v>
-      </c>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t>MOCK DATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>TOTAL AD SPEND</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="n"/>
-      <c r="C10" s="35" t="n">
-        <v>20475</v>
-      </c>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n"/>
-      <c r="F10" s="34" t="n"/>
-      <c r="G10" s="34" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>⚠  MOCK DATA — illustrative figures based on 2026 plan projections. Replace with live API data before sharing with funders.</t>
+          <t>Notes / Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL CANCELLATIONS</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="n"/>
+      <c r="C4" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="27" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>ℹ  Direct channel APIs only — Shopify (cancelReason), Amazon SP-API (IsBuyerRequestedCancellation), Mirakl/B&amp;Q (state). ManoMano, OnBuy and eBay cancellations are not yet covered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>⚠  MOCK / DRY-RUN DATA — replace with live API credentials before sharing with funders.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A12:G12"/>
+  <mergeCells count="3">
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2282,564 +1958,375 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Raw Data — Sample Transactions  |  March 2026</t>
+          <t>Paid Ad Spend  |  March 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="4" customHeight="1"/>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  eBay Finance Transactions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="47" t="inlineStr">
-        <is>
-          <t>Transaction ID</t>
-        </is>
-      </c>
-      <c r="B4" s="47" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C4" s="47" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Campaign</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Spend (£)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Conv. Value (£)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Cost / Conv (£)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>ROAS</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Performance Max — All Products</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>10673</v>
       </c>
       <c r="D4" s="47" t="inlineStr">
         <is>
-          <t>Amount (£)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E4" s="47" t="inlineStr">
         <is>
-          <t>Order ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="47" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="48" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="I4" s="48" t="n">
+        <v>18650</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.01504032258064516</v>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
-        <is>
-          <t>EBAY-FEE-001</t>
-        </is>
-      </c>
-      <c r="B5" s="48" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="C5" s="48" t="inlineStr">
-        <is>
-          <t>FINAL_VALUE_FEE</t>
-        </is>
-      </c>
-      <c r="D5" s="49" t="n">
-        <v>-45.23</v>
-      </c>
-      <c r="E5" s="48" t="inlineStr">
-        <is>
-          <t>28-12345-67890</t>
-        </is>
-      </c>
-      <c r="F5" s="48" t="inlineStr">
-        <is>
-          <t>eBay Finances API</t>
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Shopping — Spectrum Own-Label</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>4574</v>
+      </c>
+      <c r="D5" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="41" t="n">
+        <v>380000</v>
+      </c>
+      <c r="I5" s="41" t="n">
+        <v>6920</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.01821052631578947</v>
+      </c>
+      <c r="K5" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
-        <is>
-          <t>EBAY-FEE-002</t>
-        </is>
-      </c>
-      <c r="B6" s="50" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="C6" s="50" t="inlineStr">
-        <is>
-          <t>FINAL_VALUE_FEE</t>
-        </is>
-      </c>
-      <c r="D6" s="51" t="n">
-        <v>-67.81</v>
-      </c>
-      <c r="E6" s="50" t="inlineStr">
-        <is>
-          <t>28-12346-67891</t>
-        </is>
-      </c>
-      <c r="F6" s="50" t="inlineStr">
-        <is>
-          <t>eBay Finances API</t>
-        </is>
-      </c>
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Google Ads subtotal</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="12" t="n">
+        <v>15247</v>
+      </c>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="20" t="n"/>
+      <c r="K6" s="20" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
-        <is>
-          <t>EBAY-AD-001</t>
-        </is>
-      </c>
-      <c r="B7" s="48" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C7" s="48" t="inlineStr">
-        <is>
-          <t>AD_FEE</t>
-        </is>
-      </c>
-      <c r="D7" s="49" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="E7" s="48" t="inlineStr">
-        <is>
-          <t>28-12345-67890</t>
-        </is>
-      </c>
-      <c r="F7" s="48" t="inlineStr">
-        <is>
-          <t>eBay Finances API</t>
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Promoted Listings</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>2178</v>
+      </c>
+      <c r="D7" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
-        <is>
-          <t>EBAY-SHP-001</t>
-        </is>
-      </c>
-      <c r="B8" s="50" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="C8" s="50" t="inlineStr">
-        <is>
-          <t>SHIPPING_LABEL</t>
-        </is>
-      </c>
-      <c r="D8" s="51" t="n">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="E8" s="50" t="inlineStr">
-        <is>
-          <t>28-12347-67892</t>
-        </is>
-      </c>
-      <c r="F8" s="50" t="inlineStr">
-        <is>
-          <t>eBay Finances API</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="48" t="inlineStr">
-        <is>
-          <t>EBAY-SUB-001</t>
-        </is>
-      </c>
-      <c r="B9" s="48" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="C9" s="48" t="inlineStr">
-        <is>
-          <t>SUBSCRIPTION_FEE</t>
-        </is>
-      </c>
-      <c r="D9" s="49" t="n">
-        <v>-49</v>
-      </c>
-      <c r="E9" s="48" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Amazon Sponsored Products</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>3050</v>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="48" t="inlineStr">
-        <is>
-          <t>eBay Finances API</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="52" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="B10" s="52" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="C10" s="52" t="inlineStr">
-        <is>
-          <t>… (all transactions for month)</t>
-        </is>
-      </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="E10" s="52" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="F10" s="52" t="inlineStr"/>
+      <c r="E8" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="48" t="n">
+        <v>189000</v>
+      </c>
+      <c r="I8" s="48" t="n">
+        <v>3210</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.01698412698412698</v>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL AD SPEND</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="28" t="n">
+        <v>20475</v>
+      </c>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="27" t="n"/>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="27" t="n"/>
+      <c r="J10" s="27" t="n"/>
+      <c r="K10" s="27" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Amazon Settlement Line Items</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Settlement ID</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>Posted Date</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>Fee Type</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>Amount (£)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>Order ID</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="55" t="inlineStr">
-        <is>
-          <t>S-12345678</t>
-        </is>
-      </c>
-      <c r="B14" s="55" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="C14" s="55" t="inlineStr">
-        <is>
-          <t>Referral Fee</t>
-        </is>
-      </c>
-      <c r="D14" s="56" t="n">
-        <v>-52.14</v>
-      </c>
-      <c r="E14" s="55" t="inlineStr">
-        <is>
-          <t>123-4567890-1234567</t>
-        </is>
-      </c>
-      <c r="F14" s="55" t="inlineStr">
-        <is>
-          <t>SP-API Settlement</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="55" t="inlineStr">
-        <is>
-          <t>S-12345678</t>
-        </is>
-      </c>
-      <c r="B15" s="55" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="C15" s="55" t="inlineStr">
-        <is>
-          <t>FBA Fulfillment Fee</t>
-        </is>
-      </c>
-      <c r="D15" s="56" t="n">
-        <v>-11.35</v>
-      </c>
-      <c r="E15" s="55" t="inlineStr">
-        <is>
-          <t>123-4567890-1234567</t>
-        </is>
-      </c>
-      <c r="F15" s="55" t="inlineStr">
-        <is>
-          <t>SP-API Settlement</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="55" t="inlineStr">
-        <is>
-          <t>S-12345678</t>
-        </is>
-      </c>
-      <c r="B16" s="55" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="C16" s="55" t="inlineStr">
-        <is>
-          <t>Referral Fee</t>
-        </is>
-      </c>
-      <c r="D16" s="56" t="n">
-        <v>-38.7</v>
-      </c>
-      <c r="E16" s="55" t="inlineStr">
-        <is>
-          <t>123-4567891-1234568</t>
-        </is>
-      </c>
-      <c r="F16" s="55" t="inlineStr">
-        <is>
-          <t>SP-API Settlement</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="55" t="inlineStr">
-        <is>
-          <t>S-12345679</t>
-        </is>
-      </c>
-      <c r="B17" s="55" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="C17" s="55" t="inlineStr">
-        <is>
-          <t>FBA Storage Fee</t>
-        </is>
-      </c>
-      <c r="D17" s="56" t="n">
-        <v>-407</v>
-      </c>
-      <c r="E17" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="55" t="inlineStr">
-        <is>
-          <t>SP-API Settlement</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="55" t="inlineStr">
-        <is>
-          <t>S-12345679</t>
-        </is>
-      </c>
-      <c r="B18" s="55" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="C18" s="55" t="inlineStr">
-        <is>
-          <t>FBA Inbound Transport</t>
-        </is>
-      </c>
-      <c r="D18" s="56" t="n">
-        <v>-93.5</v>
-      </c>
-      <c r="E18" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="55" t="inlineStr">
-        <is>
-          <t>SP-API Settlement</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="57" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="B19" s="57" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="C19" s="57" t="inlineStr">
-        <is>
-          <t>… (all line items for month)</t>
-        </is>
-      </c>
-      <c r="D19" s="58" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="E19" s="57" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="F19" s="57" t="inlineStr"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Google Ads — Campaign Spend</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="47" t="inlineStr">
-        <is>
-          <t>Campaign ID</t>
-        </is>
-      </c>
-      <c r="B22" s="47" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C22" s="47" t="inlineStr">
-        <is>
-          <t>Campaign Name</t>
-        </is>
-      </c>
-      <c r="D22" s="47" t="inlineStr">
-        <is>
-          <t>Spend (£)</t>
-        </is>
-      </c>
-      <c r="E22" s="47" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="F22" s="47" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="48" t="inlineStr">
-        <is>
-          <t>12345001</t>
-        </is>
-      </c>
-      <c r="B23" s="48" t="inlineStr">
-        <is>
-          <t>PERFORMANCE_MAX</t>
-        </is>
-      </c>
-      <c r="C23" s="48" t="inlineStr">
-        <is>
-          <t>PMax — All Products</t>
-        </is>
-      </c>
-      <c r="D23" s="49" t="n">
-        <v>10673</v>
-      </c>
-      <c r="E23" s="48" t="n">
-        <v>1240000</v>
-      </c>
-      <c r="F23" s="48" t="n">
-        <v>18650</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="50" t="inlineStr">
-        <is>
-          <t>12345002</t>
-        </is>
-      </c>
-      <c r="B24" s="50" t="inlineStr">
-        <is>
-          <t>SHOPPING</t>
-        </is>
-      </c>
-      <c r="C24" s="50" t="inlineStr">
-        <is>
-          <t>Shopping — Spectrum Range</t>
-        </is>
-      </c>
-      <c r="D24" s="51" t="n">
-        <v>4574</v>
-      </c>
-      <c r="E24" s="50" t="n">
-        <v>380000</v>
-      </c>
-      <c r="F24" s="50" t="n">
-        <v>6920</v>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>⚠  MOCK DATA — illustrative figures based on 2026 plan projections. Replace with live API data before sharing with funders.</t>
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>ℹ  Showing campaigns with spend only. Conversions / Conv. Value / Cost-per-Conv / ROAS reflect Google Ads conversion tracking; eBay Promoted Listings and Amazon Sponsored Products do not yet feed conversion data into this report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>⚠  MOCK / DRY-RUN DATA — replace with live API credentials before sharing with funders.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A12:K12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Raw Data — Transactions  |  March 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>⚠  MOCK / DRY-RUN DATA — replace with live API credentials before sharing with funders.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
